--- a/data/elderly_welfare_facility/data.xlsx
+++ b/data/elderly_welfare_facility/data.xlsx
@@ -507,7 +507,7 @@
         <v>087-847-9555</v>
       </c>
       <c r="G3" t="str">
-        <v>http://www.kouzenkai.jp/shisetsu/kouon/f_kouonen.html</v>
+        <v>https://www.kouzenkai.jp/shisetsu/kouon/f_kouonen.html</v>
       </c>
       <c r="H3" t="str">
         <v/>

--- a/data/elderly_welfare_facility/data.xlsx
+++ b/data/elderly_welfare_facility/data.xlsx
@@ -507,7 +507,7 @@
         <v>087-847-9555</v>
       </c>
       <c r="G3" t="str">
-        <v>https://www.kouzenkai.jp/shisetsu/kouon/f_kouonen.html</v>
+        <v>https://www.kouzenkai.jp/shisetsu/kouon/</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -595,7 +595,7 @@
         <v>087-885-2828</v>
       </c>
       <c r="G5" t="str">
-        <v>http://www.koutouen.com/okamotosou/index.html</v>
+        <v>http://www.koutouen.com/okamotosou/</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -683,7 +683,7 @@
         <v>087-888-5800</v>
       </c>
       <c r="G7" t="str">
-        <v>http://www.ryuungakuen.or.jp/facility/shunkoen</v>
+        <v>https://www.ryuungakuen.or.jp/facility/shunkoen</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -727,7 +727,7 @@
         <v>087-815-1165</v>
       </c>
       <c r="G8" t="str">
-        <v>http://www.samariya.or.jp/</v>
+        <v>http://www.samariya.or.jp/samariya-matsunami/</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -815,7 +815,7 @@
         <v>087-837-0006</v>
       </c>
       <c r="G10" t="str">
-        <v>http://www.hanazono.or.jp/index9.html</v>
+        <v>https://www.hanazono.or.jp/index9.html</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -903,7 +903,7 @@
         <v>087-844-9090</v>
       </c>
       <c r="G12" t="str">
-        <v>http://www.kouzenkai.jp/shisetsu/koushiki/f_koushokuen.html</v>
+        <v>https://www.kouzenkai.jp/shisetsu/koushiki/</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -1079,7 +1079,7 @@
         <v>087-849-1333</v>
       </c>
       <c r="G16" t="str">
-        <v>http://www.sansan-kai.com/takamatsu/index.html</v>
+        <v>https://www.sansan-kai.com/takamatsu/</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -1123,7 +1123,7 @@
         <v>087-886-8168</v>
       </c>
       <c r="G17" t="str">
-        <v>http://www.kishokai.com/ichinomiya/</v>
+        <v>https://www.kishokai.com/ichinomiya/</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -1167,7 +1167,7 @@
         <v>087-832-5500</v>
       </c>
       <c r="G18" t="str">
-        <v>http://www.kouzenkai.jp/houjyuen/index.html</v>
+        <v>https://www.kouzenkai.jp/houjyuen/index.html</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -1211,7 +1211,7 @@
         <v>087-815-2000</v>
       </c>
       <c r="G19" t="str">
-        <v>http://www.saiseikai.or.jp/facilities/f03/3715-0004/</v>
+        <v>https://www.saiseikai.or.jp/facilities/f03/3715-0004/</v>
       </c>
       <c r="H19" t="str">
         <v/>
@@ -1255,7 +1255,7 @@
         <v>087-811-4450</v>
       </c>
       <c r="G20" t="str">
-        <v>http://www.sanuki-sha.or.jp/tamamo/</v>
+        <v>https://www.sanuki-sha.or.jp/tamamo/</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1299,7 +1299,7 @@
         <v>087-834-1165</v>
       </c>
       <c r="G21" t="str">
-        <v>http://www.sw-akane.jp/</v>
+        <v>https://www.sw-akane.jp/</v>
       </c>
       <c r="H21" t="str">
         <v/>
@@ -1387,7 +1387,7 @@
         <v>087-870-3500</v>
       </c>
       <c r="G23" t="str">
-        <v>http://www.yoyokai.or.jp/</v>
+        <v>https://www.yoyokai.or.jp/</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -1563,7 +1563,7 @@
         <v>087-864-9031</v>
       </c>
       <c r="G27" t="str">
-        <v>http://www.hiiragikai.com/shisetsu/</v>
+        <v>https://www.hiiragikai.com/shisetsu/</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1739,7 +1739,7 @@
         <v>087-841-7006</v>
       </c>
       <c r="G31" t="str">
-        <v>https://www.zuishou.net/rich/</v>
+        <v>https://sunrich.zuihou.net/</v>
       </c>
       <c r="H31" t="str">
         <v/>
@@ -2047,7 +2047,7 @@
         <v>087-888-5800</v>
       </c>
       <c r="G38" t="str">
-        <v>http://www.ryuungakuen.or.jp/facility/carehouse</v>
+        <v>https://www.ryuungakuen.or.jp/facility/carehouse/</v>
       </c>
       <c r="H38" t="str">
         <v/>
@@ -2091,7 +2091,7 @@
         <v>087-841-8100</v>
       </c>
       <c r="G39" t="str">
-        <v>http://kisshoh.jp/service/carehouse</v>
+        <v>https://kisshoh.jp/service/carehouse</v>
       </c>
       <c r="H39" t="str">
         <v/>
@@ -2135,7 +2135,7 @@
         <v>087-893-0502</v>
       </c>
       <c r="G40" t="str">
-        <v>https://www.kenshokai.group/institution/care/libre/</v>
+        <v>https://www.kenshokai.group/service/19987/</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -2179,7 +2179,7 @@
         <v>087-864-9000</v>
       </c>
       <c r="G41" t="str">
-        <v>http://www.hiiragikai.com/shisetsu/</v>
+        <v>https://www.hiiragikai.com/shisetsu/</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -2311,7 +2311,7 @@
         <v>087-813-5306</v>
       </c>
       <c r="G44" t="str">
-        <v>http://www.kishokai.com</v>
+        <v>https://www.kishokai.com/kocho/</v>
       </c>
       <c r="H44" t="str">
         <v/>

--- a/data/elderly_welfare_facility/data.xlsx
+++ b/data/elderly_welfare_facility/data.xlsx
@@ -1739,7 +1739,7 @@
         <v>087-841-7006</v>
       </c>
       <c r="G31" t="str">
-        <v>https://sunrich.zuihou.net/</v>
+        <v>https://sunrich.zuishou.net/</v>
       </c>
       <c r="H31" t="str">
         <v/>
